--- a/public/templates/IT_ARENA_savollar_shabloni.xlsx
+++ b/public/templates/IT_ARENA_savollar_shabloni.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Savollar" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yoʻriqnoma" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Savollar" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Yoʻriqnoma" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Savollar'!$A$1:$Q$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Savollar'!$A$1:$Q$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -211,7 +211,7 @@
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>Roʻyxatdan tanlang: Test, Toʻgʻri/Notoʻgʻri, Rasmli, Qisqa javob, Mantiqiy.</t>
+        <t>Roʻyxatdan tanlang: Test, Toʻgʻri/Notoʻgʻri, Rasmli, Qisqa javob, Mantiqiy, Moslashtirish, Koʻp bosqichli.</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
@@ -221,14 +221,18 @@
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>Test, Rasmli va Mantiqiy savollar uchun variantlar. Kamida A va B toʻldirilsin.</t>
+        <t>Test, Rasmli va Mantiqiy savollar uchun variantlar. Kamida A va B toʻldirilsin.
+Moslashtirish: har bir katakda juftlik “Chap = Oʻng” (masalan: Klaviatura = Kiritish).
+Koʻp bosqichli: har bir katak — bitta qadam “Qadam matni || variant | variant | variant”.</t>
       </text>
     </comment>
     <comment ref="J1" authorId="0" shapeId="0">
       <text>
         <t>Test/Rasmli/Mantiqiy: A, B, C yoki D.
 Toʻgʻri/Notoʻgʻri: Toʻgʻri yoki Notoʻgʻri.
-Qisqa javob: javob(lar), bir nechta boʻlsa ; bilan ajrating (masalan: 6; olti).</t>
+Qisqa javob: javob(lar), bir nechta boʻlsa ; bilan ajrating (masalan: 6; olti).
+Moslashtirish: boʻsh qoldiring (juftliklar variantlarda).
+Koʻp bosqichli: har bir qadam uchun harf, vergul bilan (masalan: A, C, B).</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
@@ -564,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1067,11 +1071,145 @@
         <v>45</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Informatika</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Saqlash qurilmalari</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Moslashtirish</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Saqlash qurilmalarini ishlash usuliga moslang.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>HDD = Magnit</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>DVD = Optik (lazer)</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>SSD = Flesh-xotira</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Magnit lenta = Magnit</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>HDD va lenta — magnit, DVD — lazer, SSD — flesh-xotira.</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Magnit, lazer yoki mikrosxema?</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>oʻrta</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P8" s="2" t="n"/>
+      <c r="Q8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Informatika</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Chiqarish qurilmalari</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Koʻp bosqichli</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Printer chop etmayapti. Muammoni bosqichma-bosqich toping.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Avval nimani tekshirasiz? || Printer yoqilgan va ulanganini | Protsessorni | Monitorni</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Ekranda “Qogʻoz tugadi” xabari. Nima qilasiz? || OT ni qayta oʻrnataman | Lotokka qogʻoz solaman</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Sahifa xira chiqyapti. Sabab? || Sichqoncha buzilgan | Siyoh yoki toner tugayapti | Internet sekin</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>A, B, B</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Nosozlik oddiy sabablardan boshlab tekshiriladi.</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Oddiydan murakkabga.</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>oʻrta</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P9" s="2" t="n"/>
+      <c r="Q9" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q7"/>
+  <autoFilter ref="A1:Q9"/>
   <dataValidations count="6">
     <dataValidation sqref="D2:D300" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Savol turi" error="Roʻyxatdan tanlang" type="list">
-      <formula1>"Test,Toʻgʻri/Notoʻgʻri,Rasmli,Qisqa javob,Mantiqiy"</formula1>
+      <formula1>"Test,Toʻgʻri/Notoʻgʻri,Rasmli,Qisqa javob,Mantiqiy,Moslashtirish,Koʻp bosqichli"</formula1>
     </dataValidation>
     <dataValidation sqref="N2:N300" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Qiyinlik" error="oson, oʻrta yoki qiyin" type="list">
       <formula1>"oson,oʻrta,qiyin"</formula1>
@@ -1103,7 +1241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1235,7 +1373,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Roʻyxatdan tanlang: Test, Toʻgʻri/Notoʻgʻri, Rasmli, Qisqa javob, Mantiqiy.</t>
+          <t>Roʻyxatdan tanlang: Test, Toʻgʻri/Notoʻgʻri, Rasmli, Qisqa javob, Mantiqiy, Moslashtirish, Koʻp bosqichli.</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1397,9 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Test, Rasmli va Mantiqiy savollar uchun variantlar. Kamida A va B toʻldirilsin.</t>
+          <t>Test, Rasmli va Mantiqiy savollar uchun variantlar. Kamida A va B toʻldirilsin.
+Moslashtirish: har bir katakda juftlik “Chap = Oʻng” (masalan: Klaviatura = Kiritish).
+Koʻp bosqichli: har bir katak — bitta qadam “Qadam matni || variant | variant | variant”.</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1449,9 @@
         <is>
           <t>Test/Rasmli/Mantiqiy: A, B, C yoki D.
 Toʻgʻri/Notoʻgʻri: Toʻgʻri yoki Notoʻgʻri.
-Qisqa javob: javob(lar), bir nechta boʻlsa ; bilan ajrating (masalan: 6; olti).</t>
+Qisqa javob: javob(lar), bir nechta boʻlsa ; bilan ajrating (masalan: 6; olti).
+Moslashtirish: boʻsh qoldiring (juftliklar variantlarda).
+Koʻp bosqichli: har bir qadam uchun harf, vergul bilan (masalan: A, C, B).</t>
         </is>
       </c>
     </row>
@@ -1469,34 +1611,34 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Moslashtirish</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>2–4 juftlik, har biri alohida katakda: “Chap = Oʻng”. Oʻng tomondagi javoblar takrorlanishi mumkin. Oʻquvchiga javoblar aralashtirib koʻrsatiladi; qisman toʻgʻri moslash qisman ball oladi.</t>
+        </is>
+      </c>
+    </row>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Koʻp bosqichli</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>2–4 qadamli zanjir: har bir katak “Qadam matni || variant | variant | variant”, “Toʻgʻri javob” ustunida har bir qadam uchun harf (A, B, A). Keyingi qadam faqat oldingisi toʻgʻri boʻlsa ochiladi; toʻliq zanjir bonus ball beradi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>Maslahatlar</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>Toʻgʻri javoblar faqat serverda saqlanadi va oʻquvchilarga javob vaqti tugaguncha yuborilmaydi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>Toʻgʻri javob har doim A boʻlib qolmasin — variantlarni aralashtiring.</t>
         </is>
       </c>
     </row>
@@ -1508,7 +1650,7 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Rasmlarni kompyuterdan yuklash: importdan keyin savolni tahrirlang → “Rasm yuklash”.</t>
+          <t>Toʻgʻri javoblar faqat serverda saqlanadi va oʻquvchilarga javob vaqti tugaguncha yuborilmaydi.</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1662,7 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Bir xil savolni ikki marta yuklamaslik uchun import oynasi takroriy savollarni belgilaydi.</t>
+          <t>Toʻgʻri javob har doim A boʻlib qolmasin — variantlarni aralashtiring.</t>
         </is>
       </c>
     </row>
@@ -1531,6 +1673,30 @@
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Rasmlarni kompyuterdan yuklash: importdan keyin savolni tahrirlang → “Rasm yuklash”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Bir xil savolni ikki marta yuklamaslik uchun import oynasi takroriy savollarni belgilaydi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>Eski .xls emas, .xlsx formatidan foydalaning. CSV (UTF-8) ham qabul qilinadi.</t>
         </is>
